--- a/output/yearly_surface_area_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_22_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497648948837</v>
+        <v>10.84497641162539</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907248992474</v>
+        <v>37.78907221861297</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.465790380169493</v>
+        <v>4.23525959612074</v>
       </c>
       <c r="C2" t="n">
-        <v>8.503898614185871</v>
+        <v>7.841218913819274</v>
       </c>
       <c r="D2" t="n">
-        <v>37.70009359078176</v>
+        <v>30.63641885872596</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18196748265093</v>
+        <v>15.07473599870977</v>
       </c>
       <c r="C3" t="n">
-        <v>17.81872083207961</v>
+        <v>23.4245002233289</v>
       </c>
       <c r="D3" t="n">
-        <v>96.08855655315656</v>
+        <v>71.13252991120264</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.72285371442869</v>
+        <v>31.07722357793278</v>
       </c>
       <c r="C4" t="n">
-        <v>43.82718101298611</v>
+        <v>59.48703864342698</v>
       </c>
       <c r="D4" t="n">
-        <v>102.4208292455485</v>
+        <v>101.1573199501829</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.35045253934967</v>
+        <v>41.52792788964008</v>
       </c>
       <c r="C5" t="n">
-        <v>71.07853378746908</v>
+        <v>110.1766361090983</v>
       </c>
       <c r="D5" t="n">
-        <v>66.3661448070844</v>
+        <v>81.58323422290995</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.44662275663685</v>
+        <v>37.91705983342032</v>
       </c>
       <c r="C6" t="n">
-        <v>81.95237135970676</v>
+        <v>146.838040628787</v>
       </c>
       <c r="D6" t="n">
-        <v>44.47807974090175</v>
+        <v>54.33973543006097</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.96704685087888</v>
+        <v>25.27214940272139</v>
       </c>
       <c r="C7" t="n">
-        <v>69.70801399234051</v>
+        <v>136.6612439265645</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>50.98706702005809</v>
+        <v>87.62098260402782</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.724849754022085</v>
+        <v>7.654253676956434</v>
       </c>
       <c r="C21" t="n">
-        <v>96.56062192527607</v>
+        <v>92.80782583309676</v>
       </c>
       <c r="D21" t="n">
-        <v>8.690455973274846</v>
+        <v>7.654253676956434</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.094108910887452</v>
+        <v>5.933683124467722</v>
       </c>
       <c r="C2" t="n">
-        <v>6.489352325071417</v>
+        <v>10.33682157801467</v>
       </c>
       <c r="D2" t="n">
-        <v>32.15616430490002</v>
+        <v>23.04750910489812</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0521968592411</v>
+        <v>14.64767574736241</v>
       </c>
       <c r="C3" t="n">
-        <v>25.89850443803086</v>
+        <v>26.83607349558656</v>
       </c>
       <c r="D3" t="n">
-        <v>102.7840758961198</v>
+        <v>78.19129590473722</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.36549755008285</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="C4" t="n">
-        <v>43.73784197189966</v>
+        <v>58.9127162364426</v>
       </c>
       <c r="D4" t="n">
-        <v>124.7683522373186</v>
+        <v>109.9763595774319</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.74377351585415</v>
+        <v>43.63868545377073</v>
       </c>
       <c r="C5" t="n">
-        <v>76.06090338652164</v>
+        <v>108.7285582453343</v>
       </c>
       <c r="D5" t="n">
-        <v>85.01935118777379</v>
+        <v>96.43216824964297</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.75104666041137</v>
+        <v>45.96739100824416</v>
       </c>
       <c r="C6" t="n">
-        <v>96.56372244201204</v>
+        <v>160.362597002491</v>
       </c>
       <c r="D6" t="n">
-        <v>54.33973543006097</v>
+        <v>64.52340436621313</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.12969817461437</v>
+        <v>34.43480072645687</v>
       </c>
       <c r="C7" t="n">
-        <v>94.2016374655942</v>
+        <v>170.4971785534308</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.28076414788136</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C8" t="n">
-        <v>71.76575718044184</v>
+        <v>130.8473340220149</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>73.55155625446676</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.915665126285734</v>
+        <v>7.828417624294302</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8720210640717</v>
+        <v>100.7908769127891</v>
       </c>
       <c r="D21" t="n">
-        <v>9.894581407857167</v>
+        <v>8.806969827331089</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.343292901316895</v>
+        <v>8.095491569219199</v>
       </c>
       <c r="C2" t="n">
-        <v>6.730862260316131</v>
+        <v>8.064075642683301</v>
       </c>
       <c r="D2" t="n">
-        <v>36.32270156172349</v>
+        <v>24.61437844087603</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.59844949342983</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="C3" t="n">
-        <v>25.38799563182252</v>
+        <v>32.61856747360027</v>
       </c>
       <c r="D3" t="n">
-        <v>103.4614818120501</v>
+        <v>77.63169971331654</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.14402347955058</v>
+        <v>28.09074706161399</v>
       </c>
       <c r="C4" t="n">
-        <v>53.27159392784043</v>
+        <v>61.70775195043327</v>
       </c>
       <c r="D4" t="n">
-        <v>141.6534310026595</v>
+        <v>119.0123654473196</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.5109193834984</v>
+        <v>43.61414176116455</v>
       </c>
       <c r="C5" t="n">
-        <v>78.09802987283378</v>
+        <v>107.3050240741764</v>
       </c>
       <c r="D5" t="n">
-        <v>106.2251015995049</v>
+        <v>110.0539176460675</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.47936458824226</v>
+        <v>51.56237117474674</v>
       </c>
       <c r="C6" t="n">
-        <v>106.8681463457866</v>
+        <v>166.1588354483642</v>
       </c>
       <c r="D6" t="n">
-        <v>65.32843748369551</v>
+        <v>75.63286138747003</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.8912155979404</v>
+        <v>42.4596064609703</v>
       </c>
       <c r="C7" t="n">
-        <v>115.4613840010589</v>
+        <v>195.4100082963978</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54996830749001</v>
+        <v>52.64033015400972</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.29182541453534</v>
+        <v>26.45319189093031</v>
       </c>
       <c r="C8" t="n">
-        <v>95.46514676095984</v>
+        <v>170.2350519163969</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>67.33905678199295</v>
+        <v>110.8265530893096</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>59.93078860574654</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.092016080455396</v>
+        <v>7.987880872894111</v>
       </c>
       <c r="C21" t="n">
-        <v>114.2997271364325</v>
+        <v>108.8348768931823</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12652211062617</v>
+        <v>9.984851091117639</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.331111018238433</v>
+        <v>7.219772617031043</v>
       </c>
       <c r="C2" t="n">
-        <v>4.414919425997907</v>
+        <v>5.547856276698725</v>
       </c>
       <c r="D2" t="n">
-        <v>29.56140512257571</v>
+        <v>20.43606021160161</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.01140542401924</v>
+        <v>19.69385894719102</v>
       </c>
       <c r="C3" t="n">
-        <v>37.08551952792326</v>
+        <v>45.62672455487051</v>
       </c>
       <c r="D3" t="n">
-        <v>113.0138869743716</v>
+        <v>84.85736281657306</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.26193101505142</v>
+        <v>20.9436237746972</v>
       </c>
       <c r="C4" t="n">
-        <v>69.65892660712818</v>
+        <v>87.32253130193681</v>
       </c>
       <c r="D4" t="n">
-        <v>131.4687803188031</v>
+        <v>117.2383473457456</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.37313054753858</v>
+        <v>29.03518835309942</v>
       </c>
       <c r="C5" t="n">
-        <v>63.83814446864886</v>
+        <v>99.27923659195872</v>
       </c>
       <c r="D5" t="n">
-        <v>68.59962083424588</v>
+        <v>74.76008767839463</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.10194719698821</v>
+        <v>26.3648345975481</v>
       </c>
       <c r="C6" t="n">
-        <v>76.03537794621123</v>
+        <v>128.6845438295592</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>67.13288976410114</v>
+        <v>119.7133333081518</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>49.56844158742145</v>
+        <v>81.69613520889833</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>45.70624611891449</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.977460860531329</v>
+        <v>4.294164458375548</v>
       </c>
       <c r="C2" t="n">
-        <v>1.939933463591697</v>
+        <v>3.178899066351172</v>
       </c>
       <c r="D2" t="n">
-        <v>20.39875379884023</v>
+        <v>14.56913593102267</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.17615911188346</v>
+        <v>22.62437584436775</v>
       </c>
       <c r="C3" t="n">
-        <v>27.16005023798801</v>
+        <v>34.09118902997049</v>
       </c>
       <c r="D3" t="n">
-        <v>112.415020874781</v>
+        <v>83.13930433414114</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.82495547567036</v>
+        <v>28.38428962518378</v>
       </c>
       <c r="C4" t="n">
-        <v>83.05978277009714</v>
+        <v>103.2759314959475</v>
       </c>
       <c r="D4" t="n">
-        <v>153.6631506687108</v>
+        <v>129.6819994970739</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.1528592088888</v>
+        <v>31.56318869153496</v>
       </c>
       <c r="C5" t="n">
-        <v>95.84311962709488</v>
+        <v>129.6397843457913</v>
       </c>
       <c r="D5" t="n">
-        <v>93.24148821084083</v>
+        <v>92.72607066611126</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>31.35603992593888</v>
       </c>
       <c r="C6" t="n">
-        <v>91.08949724313183</v>
+        <v>146.7575373170387</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>43.67304662341937</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>85.39830580161305</v>
+        <v>149.1775454080071</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>65.08987279156352</v>
+        <v>106.480356002609</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>41.26874649571891</v>
+        <v>51.03124566674919</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.720643872646163</v>
+        <v>3.953498005001906</v>
       </c>
       <c r="C2" t="n">
-        <v>5.869869523691679</v>
+        <v>6.330309196983433</v>
       </c>
       <c r="D2" t="n">
-        <v>17.10400850338793</v>
+        <v>15.2828665120101</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.44275251908209</v>
+        <v>18.58448404139212</v>
       </c>
       <c r="C3" t="n">
-        <v>16.44427404613408</v>
+        <v>22.52129233542183</v>
       </c>
       <c r="D3" t="n">
-        <v>103.1767749778185</v>
+        <v>76.14926067990385</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.14174118897259</v>
+        <v>35.53141291210056</v>
       </c>
       <c r="C4" t="n">
-        <v>74.99374363200535</v>
+        <v>94.9418752345963</v>
       </c>
       <c r="D4" t="n">
-        <v>172.9348581030756</v>
+        <v>139.8411247406199</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.52225838759286</v>
+        <v>36.61918936840603</v>
       </c>
       <c r="C5" t="n">
-        <v>125.123744906256</v>
+        <v>158.6995163914969</v>
       </c>
       <c r="D5" t="n">
-        <v>123.4056864238241</v>
+        <v>113.9563647704485</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.861722109084</v>
+        <v>36.4277485660779</v>
       </c>
       <c r="C6" t="n">
-        <v>122.1235239220778</v>
+        <v>174.4104249025586</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>58.68691426446584</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="C7" t="n">
-        <v>108.7540836856447</v>
+        <v>180.378469196675</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>88.37201959777664</v>
+        <v>148.2046334330985</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>59.3515574602409</v>
+        <v>85.19999276535516</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.304562772494764</v>
+        <v>2.335577788403162</v>
       </c>
       <c r="C2" t="n">
-        <v>2.608503650183775</v>
+        <v>2.962914571416874</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87325673516092</v>
+        <v>10.66767055434584</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.15451960466102</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="C3" t="n">
-        <v>20.50870954171587</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>98.71964040053803</v>
+        <v>74.4704721056418</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.25959197121121</v>
+        <v>39.14326271602458</v>
       </c>
       <c r="C4" t="n">
-        <v>69.90141829007715</v>
+        <v>90.19414333685872</v>
       </c>
       <c r="D4" t="n">
-        <v>185.1232558512998</v>
+        <v>147.8944011585565</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.4612101034803</v>
+        <v>38.55814108429348</v>
       </c>
       <c r="C5" t="n">
-        <v>145.9122525436822</v>
+        <v>189.5263943048468</v>
       </c>
       <c r="D5" t="n">
-        <v>134.5976102522377</v>
+        <v>119.8959383811417</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.70321876034376</v>
+        <v>30.06798693796707</v>
       </c>
       <c r="C6" t="n">
-        <v>153.3185572245202</v>
+        <v>212.3677363918531</v>
       </c>
       <c r="D6" t="n">
-        <v>55.34602682691394</v>
+        <v>57.07684802950107</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.162651323735481</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>116.2399099305266</v>
+        <v>190.3196464498782</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>72.26644850960771</v>
+        <v>107.8155328803847</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.111559385385641</v>
+        <v>2.506401888942107</v>
       </c>
       <c r="C2" t="n">
-        <v>5.888522730072368</v>
+        <v>7.776423565338985</v>
       </c>
       <c r="D2" t="n">
-        <v>11.93903383134546</v>
+        <v>10.02658930347267</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.32293824143497</v>
+        <v>13.37140373184156</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06982726018854</v>
+        <v>18.11324514335365</v>
       </c>
       <c r="D3" t="n">
-        <v>87.20373982972293</v>
+        <v>67.30371386464009</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.0005905037393</v>
+        <v>37.20332925243288</v>
       </c>
       <c r="C4" t="n">
-        <v>60.32937817367074</v>
+        <v>76.34659196845746</v>
       </c>
       <c r="D4" t="n">
-        <v>191.1600224847134</v>
+        <v>150.4214197492878</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.22393025868885</v>
+        <v>47.2956956520901</v>
       </c>
       <c r="C5" t="n">
-        <v>138.8682127657113</v>
+        <v>180.1261600366836</v>
       </c>
       <c r="D5" t="n">
-        <v>164.4918278465531</v>
+        <v>139.9235915477767</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.65166915810419</v>
+        <v>38.96360288614742</v>
       </c>
       <c r="C6" t="n">
-        <v>192.8054316370311</v>
+        <v>256.1615379828948</v>
       </c>
       <c r="D6" t="n">
-        <v>78.97374882502193</v>
+        <v>75.06933820523237</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3706719683032</v>
+        <v>241.3430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8989814352457</v>
+        <v>166.8971097219577</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>54.0265579124062</v>
+        <v>70.22343153707007</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.44249047717483</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.851977080836984</v>
+        <v>1.757328390601791</v>
       </c>
       <c r="C2" t="n">
-        <v>3.648174468981147</v>
+        <v>4.819399480147592</v>
       </c>
       <c r="D2" t="n">
-        <v>9.252972112526189</v>
+        <v>8.207410807503335</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12029730373262</v>
+        <v>11.48153940116645</v>
       </c>
       <c r="C3" t="n">
-        <v>19.02627050830318</v>
+        <v>24.08227118517426</v>
       </c>
       <c r="D3" t="n">
-        <v>79.63446502998003</v>
+        <v>61.58012474888118</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.35496036724339</v>
+        <v>33.60424216866407</v>
       </c>
       <c r="C4" t="n">
-        <v>51.66349118828415</v>
+        <v>65.15368639233958</v>
       </c>
       <c r="D4" t="n">
-        <v>191.9640738544916</v>
+        <v>152.0295224888441</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.38439710283758</v>
+        <v>51.41903600992671</v>
       </c>
       <c r="C5" t="n">
-        <v>132.5359400733194</v>
+        <v>169.7196343716674</v>
       </c>
       <c r="D5" t="n">
-        <v>184.4458499353695</v>
+        <v>152.7599427808037</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.47307319138928</v>
+        <v>46.12839763174064</v>
       </c>
       <c r="C6" t="n">
-        <v>212.2469814242307</v>
+        <v>279.0244785193945</v>
       </c>
       <c r="D6" t="n">
-        <v>98.61655689159213</v>
+        <v>89.68068928753766</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>207.1477838483727</v>
+        <v>292.0071101603543</v>
       </c>
       <c r="D7" t="n">
-        <v>46.53189593818607</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>139.6094322824177</v>
+        <v>210.6241524691107</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>65.89686940445439</v>
+        <v>81.53905557621881</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.293182710671302</v>
+        <v>2.602613163958294</v>
       </c>
       <c r="C2" t="n">
-        <v>6.131996160725578</v>
+        <v>7.443611093599316</v>
       </c>
       <c r="D2" t="n">
-        <v>11.66905321267759</v>
+        <v>11.06331487915731</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.96397843457913</v>
+        <v>8.860273030827463</v>
       </c>
       <c r="C3" t="n">
-        <v>16.71916340332318</v>
+        <v>21.61808444751476</v>
       </c>
       <c r="D3" t="n">
-        <v>70.13605599139213</v>
+        <v>55.16931224014951</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.57344813693393</v>
+        <v>28.05245890114836</v>
       </c>
       <c r="C4" t="n">
-        <v>49.11094715724244</v>
+        <v>62.71600684269474</v>
       </c>
       <c r="D4" t="n">
-        <v>188.441563091654</v>
+        <v>148.5708253267825</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.33530971762524</v>
+        <v>51.49266708774522</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7052583423396</v>
+        <v>148.2684470338746</v>
       </c>
       <c r="D5" t="n">
-        <v>205.4307071136451</v>
+        <v>166.8725660293516</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.19259644761097</v>
+        <v>54.82275530055039</v>
       </c>
       <c r="C6" t="n">
-        <v>212.4079880477272</v>
+        <v>276.4081208875768</v>
       </c>
       <c r="D6" t="n">
-        <v>124.6996298980214</v>
+        <v>108.5989675483737</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.9500383447372</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="C7" t="n">
-        <v>249.607390309343</v>
+        <v>337.7005935591135</v>
       </c>
       <c r="D7" t="n">
-        <v>58.80865097979244</v>
+        <v>55.87420709179872</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>196.3544495878833</v>
+        <v>281.8057697655257</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>107.498428371913</v>
+        <v>146.4374875654542</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>53.66723825265189</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.025566498039423</v>
+        <v>4.969606878897355</v>
       </c>
       <c r="C2" t="n">
-        <v>4.035964812158637</v>
+        <v>9.223519681398782</v>
       </c>
       <c r="D2" t="n">
-        <v>6.336199683208914</v>
+        <v>19.6055016538088</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.006111470403733</v>
+        <v>1.862375394956199</v>
       </c>
       <c r="C2" t="n">
-        <v>3.384084336538756</v>
+        <v>4.227405614486766</v>
       </c>
       <c r="D2" t="n">
-        <v>8.588328916751097</v>
+        <v>8.141633711318798</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.70581984609123</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C3" t="n">
-        <v>21.56408832378119</v>
+        <v>27.1011453757332</v>
       </c>
       <c r="D3" t="n">
-        <v>75.23623531495431</v>
+        <v>60.33821390300897</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.31064285183204</v>
+        <v>38.81143199198916</v>
       </c>
       <c r="C4" t="n">
-        <v>70.04180821178444</v>
+        <v>89.82402445235768</v>
       </c>
       <c r="D4" t="n">
-        <v>194.6570078072406</v>
+        <v>153.4589471462274</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.99425804915732</v>
+        <v>32.29949946972007</v>
       </c>
       <c r="C5" t="n">
-        <v>177.4263538500048</v>
+        <v>228.91902093775</v>
       </c>
       <c r="D5" t="n">
-        <v>186.384801651257</v>
+        <v>152.5881369325605</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.94344384824796</v>
+        <v>17.46921864936775</v>
       </c>
       <c r="C6" t="n">
-        <v>210.1941469746506</v>
+        <v>276.6093791669473</v>
       </c>
       <c r="D6" t="n">
-        <v>95.63793435690729</v>
+        <v>85.21275548551041</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.066619975168541</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>138.0386359556228</v>
+        <v>198.1647923545144</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>79.19267856306895</v>
+        <v>107.8989814352457</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>40.93593402397924</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.20360698987336</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.972953032637593</v>
+        <v>5.839435344860028</v>
       </c>
       <c r="C2" t="n">
-        <v>4.161628518302229</v>
+        <v>7.087236676957724</v>
       </c>
       <c r="D2" t="n">
-        <v>12.93354425574748</v>
+        <v>21.48063976892021</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.6814150222053</v>
+        <v>10.55869655917445</v>
       </c>
       <c r="C3" t="n">
-        <v>10.32798584867645</v>
+        <v>23.24287689804324</v>
       </c>
       <c r="D3" t="n">
-        <v>8.713010875190442</v>
+        <v>19.6055016538088</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3993607214725</v>
+        <v>13.39620378741447</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14959436535605</v>
+        <v>70.13306688705225</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576395378996765</v>
+        <v>1.576023974989938</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.903428872085318</v>
+        <v>4.504258467084366</v>
       </c>
       <c r="C2" t="n">
-        <v>2.581014714464864</v>
+        <v>10.37510973848029</v>
       </c>
       <c r="D2" t="n">
-        <v>17.38478834680252</v>
+        <v>28.33029350145021</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64062358698343</v>
+        <v>16.31664684458199</v>
       </c>
       <c r="C3" t="n">
-        <v>14.08807955594173</v>
+        <v>25.99177046993431</v>
       </c>
       <c r="D3" t="n">
-        <v>17.47020039707199</v>
+        <v>32.90818304635308</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.49470303194916</v>
+        <v>12.35431311024186</v>
       </c>
       <c r="C4" t="n">
-        <v>16.54048532115026</v>
+        <v>35.96534539737765</v>
       </c>
       <c r="D4" t="n">
-        <v>19.64182631886593</v>
+        <v>25.34676222824415</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44571841449002</v>
+        <v>15.43564287195306</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17085010189167</v>
+        <v>86.11463918036968</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251730192524214</v>
+        <v>3.249609025674328</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80467326458389</v>
+        <v>5.687264450701772</v>
       </c>
       <c r="C2" t="n">
-        <v>4.431609136970102</v>
+        <v>6.576727870749383</v>
       </c>
       <c r="D2" t="n">
-        <v>24.52307590438108</v>
+        <v>28.39116185911351</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.89311267342411</v>
+        <v>15.87486037767093</v>
       </c>
       <c r="C3" t="n">
-        <v>11.6042578641973</v>
+        <v>34.54770171244526</v>
       </c>
       <c r="D3" t="n">
-        <v>27.32203860918873</v>
+        <v>47.93383165985052</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.95562573132642</v>
+        <v>22.92184539875453</v>
       </c>
       <c r="C4" t="n">
-        <v>27.75891633757857</v>
+        <v>52.81213600225291</v>
       </c>
       <c r="D4" t="n">
-        <v>23.80247308946392</v>
+        <v>36.13126075939537</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.31464229144449</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C5" t="n">
-        <v>19.9785657814226</v>
+        <v>39.56443248114646</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86967390170921</v>
+        <v>32.0295188510522</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74625423642066</v>
+        <v>16.72185262163793</v>
       </c>
       <c r="C21" t="n">
-        <v>102.152150842166</v>
+        <v>102.0033009919914</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023876270926198</v>
+        <v>4.180463155409482</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.774639996379739</v>
+        <v>5.40157586876595</v>
       </c>
       <c r="C2" t="n">
-        <v>6.574764375340889</v>
+        <v>5.785439221126453</v>
       </c>
       <c r="D2" t="n">
-        <v>26.88810612391164</v>
+        <v>23.70822530985622</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.82086425393735</v>
+        <v>17.76472470834603</v>
       </c>
       <c r="C3" t="n">
-        <v>14.89311267342411</v>
+        <v>29.38861752662827</v>
       </c>
       <c r="D3" t="n">
-        <v>39.87859174650544</v>
+        <v>58.84595739255382</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.85276320655876</v>
+        <v>27.10801760966293</v>
       </c>
       <c r="C4" t="n">
-        <v>28.49915410658066</v>
+        <v>71.25426662652924</v>
       </c>
       <c r="D4" t="n">
-        <v>31.46010518258904</v>
+        <v>51.16574510223102</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.78283813537898</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="C5" t="n">
-        <v>36.98734475749859</v>
+        <v>69.90043654237292</v>
       </c>
       <c r="D5" t="n">
-        <v>31.857713002809</v>
+        <v>37.20823799095412</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="C6" t="n">
-        <v>22.70193391300324</v>
+        <v>38.40007970390975</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.37951975538279</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08312859154775</v>
+        <v>18.0360012866872</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9708865258115</v>
+        <v>117.6634369655308</v>
       </c>
       <c r="D21" t="n">
-        <v>6.888810892018189</v>
+        <v>6.012000428895734</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.235079669671493</v>
+        <v>5.353470231257857</v>
       </c>
       <c r="C2" t="n">
-        <v>3.695298358784994</v>
+        <v>7.037167544041137</v>
       </c>
       <c r="D2" t="n">
-        <v>38.36964552507809</v>
+        <v>19.90297120819559</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1890196430299</v>
+        <v>16.09084487260522</v>
       </c>
       <c r="C3" t="n">
-        <v>19.85584731839174</v>
+        <v>23.9006478598886</v>
       </c>
       <c r="D3" t="n">
-        <v>48.39525308084652</v>
+        <v>60.00441968356505</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.0840136964045</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="C4" t="n">
-        <v>27.86101809882023</v>
+        <v>60.57186985661971</v>
       </c>
       <c r="D4" t="n">
-        <v>37.86699070050372</v>
+        <v>59.48703864342698</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.9785657814226</v>
+        <v>19.29134238844983</v>
       </c>
       <c r="C5" t="n">
-        <v>34.04210164475816</v>
+        <v>75.49639845657973</v>
       </c>
       <c r="D5" t="n">
-        <v>29.28062527916113</v>
+        <v>37.77274292089604</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>28.29691407950582</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>31.71830482880595</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>17.66654993792135</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.072849524854266</v>
+        <v>7.044199697983129</v>
       </c>
       <c r="C21" t="n">
-        <v>67.19207048611553</v>
+        <v>66.03937216859184</v>
       </c>
       <c r="D21" t="n">
-        <v>5.3046371436407</v>
+        <v>4.402624811239455</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.289656630481814</v>
+        <v>4.28434698133308</v>
       </c>
       <c r="C2" t="n">
-        <v>4.98335134675681</v>
+        <v>5.132576997802325</v>
       </c>
       <c r="D2" t="n">
-        <v>39.44662275663684</v>
+        <v>22.63124807829747</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.81166867170063</v>
+        <v>17.71563732313369</v>
       </c>
       <c r="C3" t="n">
-        <v>16.27737693641212</v>
+        <v>26.16848505669873</v>
       </c>
       <c r="D3" t="n">
-        <v>70.00352005131882</v>
+        <v>62.22316949516284</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.97588258021711</v>
+        <v>28.06522162130357</v>
       </c>
       <c r="C4" t="n">
-        <v>42.10421379203296</v>
+        <v>60.24003913258429</v>
       </c>
       <c r="D4" t="n">
-        <v>55.28810371236337</v>
+        <v>77.13788061808039</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.99806186678729</v>
+        <v>27.61165418194155</v>
       </c>
       <c r="C5" t="n">
-        <v>45.13585070274711</v>
+        <v>97.51209072431446</v>
       </c>
       <c r="D5" t="n">
-        <v>36.86462629446773</v>
+        <v>50.95270585040947</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.01136436629024</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C6" t="n">
-        <v>44.03531152628644</v>
+        <v>90.48572240502003</v>
       </c>
       <c r="D6" t="n">
-        <v>33.48937768726721</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>31.73990327829938</v>
+        <v>53.29908286355933</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>21.94696992843745</v>
+        <v>26.8704346652352</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.301920568236693</v>
+        <v>7.261159380489604</v>
       </c>
       <c r="C21" t="n">
-        <v>77.58290603751486</v>
+        <v>75.33452857257964</v>
       </c>
       <c r="D21" t="n">
-        <v>6.389180497207106</v>
+        <v>5.445869535367202</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.094288837336698</v>
+        <v>4.208752408106076</v>
       </c>
       <c r="C2" t="n">
-        <v>4.511130701014094</v>
+        <v>6.270422587024377</v>
       </c>
       <c r="D2" t="n">
-        <v>38.21649288321559</v>
+        <v>26.10172621280995</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.06063167795183</v>
+        <v>16.07120991852029</v>
       </c>
       <c r="C3" t="n">
-        <v>18.25068982194821</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="D3" t="n">
-        <v>86.22199212547612</v>
+        <v>66.48886327011523</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.53592073999429</v>
+        <v>31.74088502600363</v>
       </c>
       <c r="C4" t="n">
-        <v>41.35121330287565</v>
+        <v>63.32861741014475</v>
       </c>
       <c r="D4" t="n">
-        <v>79.14162768244812</v>
+        <v>89.47943100816704</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.41654843070369</v>
+        <v>35.17111150464198</v>
       </c>
       <c r="C5" t="n">
-        <v>64.47628047640929</v>
+        <v>105.3169849730766</v>
       </c>
       <c r="D5" t="n">
-        <v>49.06284151973436</v>
+        <v>67.15154297048184</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.10823859384119</v>
+        <v>29.02144388523996</v>
       </c>
       <c r="C6" t="n">
-        <v>59.89446394068941</v>
+        <v>125.4644113596297</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>44.19631814978292</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>49.58611304609789</v>
+        <v>94.14175085563514</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>33.71321616383547</v>
+        <v>50.48637569089222</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>29.17656002251095</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.519804631531671</v>
+        <v>7.464918445688183</v>
       </c>
       <c r="C21" t="n">
-        <v>87.41772884155567</v>
+        <v>83.98033251399207</v>
       </c>
       <c r="D21" t="n">
-        <v>7.519804631531671</v>
+        <v>6.53180363997716</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_22_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641162539</v>
+        <v>10.84497617343429</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907221861297</v>
+        <v>37.78907138864153</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.23525959612074</v>
+        <v>7.547676350249478</v>
       </c>
       <c r="C2" t="n">
-        <v>7.841218913819274</v>
+        <v>7.680212290322798</v>
       </c>
       <c r="D2" t="n">
-        <v>30.63641885872596</v>
+        <v>20.775744917271</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07473599870977</v>
+        <v>21.58372327786613</v>
       </c>
       <c r="C3" t="n">
-        <v>23.4245002233289</v>
+        <v>32.96217917008666</v>
       </c>
       <c r="D3" t="n">
-        <v>71.13252991120264</v>
+        <v>59.2042953046039</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.07722357793278</v>
+        <v>43.46982484864026</v>
       </c>
       <c r="C4" t="n">
-        <v>59.48703864342698</v>
+        <v>74.30455674362409</v>
       </c>
       <c r="D4" t="n">
-        <v>101.1573199501829</v>
+        <v>73.89614969865741</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.52792788964008</v>
+        <v>52.2535215585365</v>
       </c>
       <c r="C5" t="n">
-        <v>110.1766361090983</v>
+        <v>115.7971417159113</v>
       </c>
       <c r="D5" t="n">
-        <v>81.58323422290995</v>
+        <v>56.10688129770523</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.91705983342032</v>
+        <v>47.01393406097126</v>
       </c>
       <c r="C6" t="n">
-        <v>146.838040628787</v>
+        <v>128.966305420678</v>
       </c>
       <c r="D6" t="n">
-        <v>54.33973543006097</v>
+        <v>42.78751019418875</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.27214940272139</v>
+        <v>32.57831581772616</v>
       </c>
       <c r="C7" t="n">
-        <v>136.6612439265645</v>
+        <v>107.5563514864636</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="C8" t="n">
-        <v>87.62098260402782</v>
+        <v>61.00089360337556</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.654253676956434</v>
+        <v>7.697757913674099</v>
       </c>
       <c r="C21" t="n">
-        <v>92.80782583309676</v>
+        <v>95.25975418171699</v>
       </c>
       <c r="D21" t="n">
-        <v>7.654253676956434</v>
+        <v>8.659977652883361</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.933683124467722</v>
+        <v>8.433212779480101</v>
       </c>
       <c r="C2" t="n">
-        <v>10.33682157801467</v>
+        <v>10.82867717784232</v>
       </c>
       <c r="D2" t="n">
-        <v>23.04750910489812</v>
+        <v>28.49522711576367</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.64767574736241</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="C3" t="n">
-        <v>26.83607349558656</v>
+        <v>31.1803070868787</v>
       </c>
       <c r="D3" t="n">
-        <v>78.19129590473722</v>
+        <v>61.30032665317084</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.50740899884213</v>
+        <v>42.29565459436108</v>
       </c>
       <c r="C4" t="n">
-        <v>58.9127162364426</v>
+        <v>77.50799950258143</v>
       </c>
       <c r="D4" t="n">
-        <v>109.9763595774319</v>
+        <v>84.70617367011906</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.63868545377073</v>
+        <v>57.92311455056183</v>
       </c>
       <c r="C5" t="n">
-        <v>108.7285582453343</v>
+        <v>126.130036303109</v>
       </c>
       <c r="D5" t="n">
-        <v>96.43216824964297</v>
+        <v>67.05336820005716</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.96739100824416</v>
+        <v>57.80137783523521</v>
       </c>
       <c r="C6" t="n">
-        <v>160.362597002491</v>
+        <v>153.9223320626319</v>
       </c>
       <c r="D6" t="n">
-        <v>64.52340436621313</v>
+        <v>49.75104666041137</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.43480072645687</v>
+        <v>43.77711188006952</v>
       </c>
       <c r="C7" t="n">
-        <v>170.4971785534308</v>
+        <v>145.5244622005047</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>41.56130731158447</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.3600647277471</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="C8" t="n">
-        <v>130.8473340220149</v>
+        <v>98.63619184567703</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>12.42499894494763</v>
       </c>
       <c r="C9" t="n">
-        <v>73.55155625446676</v>
+        <v>53.91562042182632</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.828417624294302</v>
+        <v>7.878757788752676</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7908769127891</v>
+        <v>103.4086959773789</v>
       </c>
       <c r="D21" t="n">
-        <v>8.806969827331089</v>
+        <v>9.848447235940844</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.095491569219199</v>
+        <v>9.729119749085891</v>
       </c>
       <c r="C2" t="n">
-        <v>8.064075642683301</v>
+        <v>11.1722888743287</v>
       </c>
       <c r="D2" t="n">
-        <v>24.61437844087603</v>
+        <v>31.33247798103695</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64062358698343</v>
+        <v>25.14746744428205</v>
       </c>
       <c r="C3" t="n">
-        <v>32.61856747360027</v>
+        <v>35.9516009295182</v>
       </c>
       <c r="D3" t="n">
-        <v>77.63169971331654</v>
+        <v>67.11718180083319</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.09074706161399</v>
+        <v>42.34670547498192</v>
       </c>
       <c r="C4" t="n">
-        <v>61.70775195043327</v>
+        <v>76.67842269249287</v>
       </c>
       <c r="D4" t="n">
-        <v>119.0123654473196</v>
+        <v>92.07026319967437</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>60.42657119639119</v>
       </c>
       <c r="C5" t="n">
-        <v>107.3050240741764</v>
+        <v>131.9714351433775</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0539176460675</v>
+        <v>78.80979695841272</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.56237117474674</v>
+        <v>65.9322123218073</v>
       </c>
       <c r="C6" t="n">
-        <v>166.1588354483642</v>
+        <v>174.3701732466845</v>
       </c>
       <c r="D6" t="n">
-        <v>75.63286138747003</v>
+        <v>56.67433147075987</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.4596064609703</v>
+        <v>54.07760879302705</v>
       </c>
       <c r="C7" t="n">
-        <v>195.4100082963978</v>
+        <v>177.5637985285993</v>
       </c>
       <c r="D7" t="n">
-        <v>52.64033015400972</v>
+        <v>45.15450390912779</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.45319189093031</v>
+        <v>34.63115026730623</v>
       </c>
       <c r="C8" t="n">
-        <v>170.2350519163969</v>
+        <v>138.4411525143639</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>17.86093598336221</v>
       </c>
       <c r="C9" t="n">
-        <v>110.8265530893096</v>
+        <v>83.31405542549703</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>59.93078860574654</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.987880872894111</v>
+        <v>8.042845019806037</v>
       </c>
       <c r="C21" t="n">
-        <v>108.8348768931823</v>
+        <v>111.5944746498088</v>
       </c>
       <c r="D21" t="n">
-        <v>9.984851091117639</v>
+        <v>11.0589119022333</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.219772617031043</v>
+        <v>8.90739692063131</v>
       </c>
       <c r="C2" t="n">
-        <v>5.547856276698725</v>
+        <v>7.596763735461819</v>
       </c>
       <c r="D2" t="n">
-        <v>20.43606021160161</v>
+        <v>25.71000887881547</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69385894719102</v>
+        <v>29.72732048459342</v>
       </c>
       <c r="C3" t="n">
-        <v>45.62672455487051</v>
+        <v>53.38744015694155</v>
       </c>
       <c r="D3" t="n">
-        <v>84.85736281657306</v>
+        <v>72.08482518432206</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.9436237746972</v>
+        <v>29.02242563294421</v>
       </c>
       <c r="C4" t="n">
-        <v>87.32253130193681</v>
+        <v>107.8322225913569</v>
       </c>
       <c r="D4" t="n">
-        <v>117.2383473457456</v>
+        <v>88.42012523528473</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.03518835309942</v>
+        <v>37.13460691313561</v>
       </c>
       <c r="C5" t="n">
-        <v>99.27923659195872</v>
+        <v>104.1879751131928</v>
       </c>
       <c r="D5" t="n">
-        <v>74.76008767839463</v>
+        <v>55.02695882303374</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.3648345975481</v>
+        <v>33.56988099901544</v>
       </c>
       <c r="C6" t="n">
-        <v>128.6845438295592</v>
+        <v>116.9310603143164</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>29.7057220351</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="C7" t="n">
-        <v>119.7133333081518</v>
+        <v>97.31574118346508</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>81.69613520889833</v>
+        <v>61.33468782281948</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>45.70624611891449</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.294164458375548</v>
+        <v>5.361324212891832</v>
       </c>
       <c r="C2" t="n">
-        <v>3.178899066351172</v>
+        <v>3.676645152404305</v>
       </c>
       <c r="D2" t="n">
-        <v>14.56913593102267</v>
+        <v>17.73330878181013</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.62437584436775</v>
+        <v>30.9643225919444</v>
       </c>
       <c r="C3" t="n">
-        <v>34.09118902997049</v>
+        <v>42.45077073163208</v>
       </c>
       <c r="D3" t="n">
-        <v>83.13930433414114</v>
+        <v>75.6092994425681</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>40.93004353775377</v>
       </c>
       <c r="C4" t="n">
-        <v>103.2759314959475</v>
+        <v>122.956045975279</v>
       </c>
       <c r="D4" t="n">
-        <v>129.6819994970739</v>
+        <v>102.6250327680318</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.56318869153496</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="C5" t="n">
-        <v>129.6397843457913</v>
+        <v>149.5938064346078</v>
       </c>
       <c r="D5" t="n">
-        <v>92.72607066611126</v>
+        <v>68.74688298988291</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.35603992593888</v>
+        <v>39.88939097125216</v>
       </c>
       <c r="C6" t="n">
-        <v>146.7575373170387</v>
+        <v>141.5248220534032</v>
       </c>
       <c r="D6" t="n">
-        <v>43.67304662341937</v>
+        <v>36.02523200733671</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>21.61906619521901</v>
       </c>
       <c r="C7" t="n">
-        <v>149.1775454080071</v>
+        <v>126.8398398932794</v>
       </c>
       <c r="D7" t="n">
-        <v>31.68001666834032</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>106.480356002609</v>
+        <v>82.69751786723006</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>51.03124566674919</v>
+        <v>40.82499653339935</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.953498005001906</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C2" t="n">
-        <v>6.330309196983433</v>
+        <v>5.228788272818512</v>
       </c>
       <c r="D2" t="n">
-        <v>15.2828665120101</v>
+        <v>16.30781111524377</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.58448404139212</v>
+        <v>24.78422079371073</v>
       </c>
       <c r="C3" t="n">
-        <v>22.52129233542183</v>
+        <v>27.61165418194155</v>
       </c>
       <c r="D3" t="n">
-        <v>76.14926067990385</v>
+        <v>72.30080967925635</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.53141291210056</v>
+        <v>49.39172700065703</v>
       </c>
       <c r="C4" t="n">
-        <v>94.9418752345963</v>
+        <v>114.2263453891164</v>
       </c>
       <c r="D4" t="n">
-        <v>139.8411247406199</v>
+        <v>114.8389559565664</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.61918936840603</v>
+        <v>50.80544369477245</v>
       </c>
       <c r="C5" t="n">
-        <v>158.6995163914969</v>
+        <v>188.7655398340555</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9563647704485</v>
+        <v>86.39379797371933</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.4277485660779</v>
+        <v>47.81896717845365</v>
       </c>
       <c r="C6" t="n">
-        <v>174.4104249025586</v>
+        <v>186.002901794305</v>
       </c>
       <c r="D6" t="n">
-        <v>58.68691426446584</v>
+        <v>46.57116584635595</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>31.68001666834032</v>
       </c>
       <c r="C7" t="n">
-        <v>180.378469196675</v>
+        <v>164.0893112878119</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C8" t="n">
-        <v>148.2046334330985</v>
+        <v>121.2507502130023</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>85.19999276535516</v>
+        <v>66.89530681967339</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>44.4142661401257</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.335577788403162</v>
+        <v>3.970187715974101</v>
       </c>
       <c r="C2" t="n">
-        <v>2.962914571416874</v>
+        <v>2.45633275602552</v>
       </c>
       <c r="D2" t="n">
-        <v>10.66767055434584</v>
+        <v>11.36372967665683</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.35868206941536</v>
+        <v>26.1488501026138</v>
       </c>
       <c r="C3" t="n">
-        <v>24.90203051822035</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D3" t="n">
-        <v>74.4704721056418</v>
+        <v>71.63812997888975</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.14326271602458</v>
+        <v>54.10117073792898</v>
       </c>
       <c r="C4" t="n">
-        <v>90.19414333685872</v>
+        <v>108.9553419650153</v>
       </c>
       <c r="D4" t="n">
-        <v>147.8944011585565</v>
+        <v>123.6069447031947</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.55814108429348</v>
+        <v>52.62167694762905</v>
       </c>
       <c r="C5" t="n">
-        <v>189.5263943048468</v>
+        <v>225.2129233542184</v>
       </c>
       <c r="D5" t="n">
-        <v>119.8959383811417</v>
+        <v>91.52342972840891</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.06798693796707</v>
+        <v>39.08435785376978</v>
       </c>
       <c r="C6" t="n">
-        <v>212.3677363918531</v>
+        <v>221.8671271781452</v>
       </c>
       <c r="D6" t="n">
-        <v>57.07684802950107</v>
+        <v>46.16864928761476</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>190.3196464498782</v>
+        <v>166.5446622961332</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8155328803847</v>
+        <v>86.11890861653021</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.506401888942107</v>
+        <v>4.208752408106076</v>
       </c>
       <c r="C2" t="n">
-        <v>7.776423565338985</v>
+        <v>6.351907646476863</v>
       </c>
       <c r="D2" t="n">
-        <v>10.02658930347267</v>
+        <v>18.2673795329204</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.37140373184156</v>
+        <v>20.09637550593221</v>
       </c>
       <c r="C3" t="n">
-        <v>18.11324514335365</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="D3" t="n">
-        <v>67.30371386464009</v>
+        <v>65.49238935030472</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.20332925243288</v>
+        <v>52.54411887899354</v>
       </c>
       <c r="C4" t="n">
-        <v>76.34659196845746</v>
+        <v>88.61156603761286</v>
       </c>
       <c r="D4" t="n">
-        <v>150.4214197492878</v>
+        <v>129.4650332544354</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.2956956520901</v>
+        <v>64.54991155422779</v>
       </c>
       <c r="C5" t="n">
-        <v>180.1261600366836</v>
+        <v>213.5792130588937</v>
       </c>
       <c r="D5" t="n">
-        <v>139.9235915477767</v>
+        <v>109.7839370273996</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>51.07935130425731</v>
       </c>
       <c r="C6" t="n">
-        <v>256.1615379828948</v>
+        <v>286.4307832002325</v>
       </c>
       <c r="D6" t="n">
-        <v>75.06933820523237</v>
+        <v>59.53219903782235</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>241.3430381349934</v>
+        <v>232.1803868112579</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>166.8971097219577</v>
+        <v>140.6942634956104</v>
       </c>
       <c r="D8" t="n">
         <v>33.12907627980861</v>
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>70.22343153707007</v>
+        <v>57.90937008270233</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.757328390601791</v>
+        <v>3.039490892348125</v>
       </c>
       <c r="C2" t="n">
-        <v>4.819399480147592</v>
+        <v>4.635812659453438</v>
       </c>
       <c r="D2" t="n">
-        <v>8.207410807503335</v>
+        <v>14.09102479905447</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.48153940116645</v>
+        <v>17.87762569433442</v>
       </c>
       <c r="C3" t="n">
-        <v>24.08227118517426</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D3" t="n">
-        <v>61.58012474888118</v>
+        <v>65.65928646002668</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.60424216866407</v>
+        <v>48.26860762699868</v>
       </c>
       <c r="C4" t="n">
-        <v>65.15368639233958</v>
+        <v>72.22423335832511</v>
       </c>
       <c r="D4" t="n">
-        <v>152.0295224888441</v>
+        <v>131.8644246436146</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.41903600992671</v>
+        <v>71.42214548395546</v>
       </c>
       <c r="C5" t="n">
-        <v>169.7196343716674</v>
+        <v>201.9945901487813</v>
       </c>
       <c r="D5" t="n">
-        <v>152.7599427808037</v>
+        <v>122.1785017935156</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.12839763174064</v>
+        <v>60.01521890831177</v>
       </c>
       <c r="C6" t="n">
-        <v>279.0244785193945</v>
+        <v>317.5453131909266</v>
       </c>
       <c r="D6" t="n">
-        <v>89.68068928753766</v>
+        <v>70.96366930607222</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.03153909972291</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>292.0071101603543</v>
+        <v>293.6240486292488</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>210.6241524691107</v>
+        <v>182.0012981517949</v>
       </c>
       <c r="D8" t="n">
         <v>34.13045893814036</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>81.53905557621881</v>
+        <v>66.22968187619405</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.602613163958294</v>
+        <v>4.825289966373073</v>
       </c>
       <c r="C2" t="n">
-        <v>7.443611093599316</v>
+        <v>15.89547707946011</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06331487915731</v>
+        <v>17.21298249855933</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.860273030827463</v>
+        <v>14.27461161974862</v>
       </c>
       <c r="C3" t="n">
-        <v>21.61808444751476</v>
+        <v>19.68895020866978</v>
       </c>
       <c r="D3" t="n">
-        <v>55.16931224014951</v>
+        <v>62.03172869283472</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.05245890114836</v>
+        <v>41.40226418349649</v>
       </c>
       <c r="C4" t="n">
-        <v>62.71600684269474</v>
+        <v>62.83087132409162</v>
       </c>
       <c r="D4" t="n">
-        <v>148.5708253267825</v>
+        <v>133.4470019428604</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.49266708774522</v>
+        <v>71.61849502480483</v>
       </c>
       <c r="C5" t="n">
-        <v>148.2684470338746</v>
+        <v>172.3458094805276</v>
       </c>
       <c r="D5" t="n">
-        <v>166.8725660293516</v>
+        <v>136.1193191938203</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.82275530055039</v>
+        <v>73.45927197026759</v>
       </c>
       <c r="C6" t="n">
-        <v>276.4081208875768</v>
+        <v>320.1214191668702</v>
       </c>
       <c r="D6" t="n">
-        <v>108.5989675483737</v>
+        <v>86.17879522648927</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.14670668075605</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="C7" t="n">
-        <v>337.7005935591135</v>
+        <v>362.972742961835</v>
       </c>
       <c r="D7" t="n">
-        <v>55.87420709179872</v>
+        <v>49.28667999630262</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>281.8057697655257</v>
+        <v>259.7753512822273</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>146.4374875654542</v>
+        <v>123.5843645059969</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>53.66723825265189</v>
+        <v>47.26133448244146</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.969606878897355</v>
+        <v>6.841799750896022</v>
       </c>
       <c r="C2" t="n">
-        <v>9.223519681398782</v>
+        <v>3.264311116620644</v>
       </c>
       <c r="D2" t="n">
-        <v>19.6055016538088</v>
+        <v>8.681594948654544</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.862375394956199</v>
+        <v>3.491094836301658</v>
       </c>
       <c r="C2" t="n">
-        <v>4.227405614486766</v>
+        <v>9.155779089805753</v>
       </c>
       <c r="D2" t="n">
-        <v>8.141633711318798</v>
+        <v>12.8059170541954</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.18348900970292</v>
+        <v>19.24716374175872</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1011453757332</v>
+        <v>34.8127735925919</v>
       </c>
       <c r="D3" t="n">
-        <v>60.33821390300897</v>
+        <v>67.81913140936966</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.81143199198916</v>
+        <v>55.58164627593317</v>
       </c>
       <c r="C4" t="n">
-        <v>89.82402445235768</v>
+        <v>93.6145523384546</v>
       </c>
       <c r="D4" t="n">
-        <v>153.4589471462274</v>
+        <v>136.1271731754542</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.29949946972007</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="C5" t="n">
-        <v>228.91902093775</v>
+        <v>265.7836472322178</v>
       </c>
       <c r="D5" t="n">
-        <v>152.5881369325605</v>
+        <v>123.7492981203105</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.46921864936775</v>
+        <v>22.78243722475149</v>
       </c>
       <c r="C6" t="n">
-        <v>276.6093791669473</v>
+        <v>298.6672865859647</v>
       </c>
       <c r="D6" t="n">
-        <v>85.21275548551041</v>
+        <v>70.44039777970866</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>198.1647923545144</v>
+        <v>182.6541603751191</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8989814352457</v>
+        <v>91.04237335332795</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>36.0546844384641</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.839435344860028</v>
+        <v>7.214863878509809</v>
       </c>
       <c r="C2" t="n">
-        <v>7.087236676957724</v>
+        <v>7.652723354603888</v>
       </c>
       <c r="D2" t="n">
-        <v>21.48063976892021</v>
+        <v>12.15207308316702</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.55869655917445</v>
+        <v>14.52986602285279</v>
       </c>
       <c r="C3" t="n">
-        <v>23.24287689804324</v>
+        <v>8.222137023067038</v>
       </c>
       <c r="D3" t="n">
-        <v>19.6055016538088</v>
+        <v>10.42616061910113</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39620378741447</v>
+        <v>13.39877724830932</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13306688705225</v>
+        <v>70.14653971173701</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576023974989938</v>
+        <v>1.576326735095213</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.504258467084366</v>
+        <v>4.774239085752239</v>
       </c>
       <c r="C2" t="n">
-        <v>10.37510973848029</v>
+        <v>6.924266558052754</v>
       </c>
       <c r="D2" t="n">
-        <v>28.33029350145021</v>
+        <v>13.27519245682537</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.31664684458199</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="C3" t="n">
-        <v>25.99177046993431</v>
+        <v>21.97642235956485</v>
       </c>
       <c r="D3" t="n">
-        <v>32.90818304635308</v>
+        <v>18.11324514335365</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.35431311024186</v>
+        <v>16.83402788472006</v>
       </c>
       <c r="C4" t="n">
-        <v>35.96534539737765</v>
+        <v>13.27322896141688</v>
       </c>
       <c r="D4" t="n">
-        <v>25.34676222824415</v>
+        <v>20.53521672973053</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43564287195306</v>
+        <v>15.4436413288139</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11463918036968</v>
+        <v>86.15926215022493</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249609025674328</v>
+        <v>3.251292911329243</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.687264450701772</v>
+        <v>5.32794479094744</v>
       </c>
       <c r="C2" t="n">
-        <v>6.576727870749383</v>
+        <v>8.70417514585222</v>
       </c>
       <c r="D2" t="n">
-        <v>28.39116185911351</v>
+        <v>20.32021398250048</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.87486037767093</v>
+        <v>18.38813450054276</v>
       </c>
       <c r="C3" t="n">
-        <v>34.54770171244526</v>
+        <v>24.99038781160256</v>
       </c>
       <c r="D3" t="n">
-        <v>47.93383165985052</v>
+        <v>24.52896639060656</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.92184539875453</v>
+        <v>30.00515508489526</v>
       </c>
       <c r="C4" t="n">
-        <v>52.81213600225291</v>
+        <v>37.8414652601933</v>
       </c>
       <c r="D4" t="n">
-        <v>36.13126075939537</v>
+        <v>25.00216878405352</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.06920536538279</v>
+        <v>14.75075925630833</v>
       </c>
       <c r="C5" t="n">
-        <v>39.56443248114646</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="D5" t="n">
-        <v>32.0295188510522</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72185262163793</v>
+        <v>16.74092802761664</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0033009919914</v>
+        <v>102.1196609684615</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180463155409482</v>
+        <v>5.022278408284992</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.40157586876595</v>
+        <v>7.143196296099792</v>
       </c>
       <c r="C2" t="n">
-        <v>5.785439221126453</v>
+        <v>6.299875018151782</v>
       </c>
       <c r="D2" t="n">
-        <v>23.70822530985622</v>
+        <v>20.38991806950201</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.76472470834603</v>
+        <v>18.31941216124548</v>
       </c>
       <c r="C3" t="n">
-        <v>29.38861752662827</v>
+        <v>30.05129722699487</v>
       </c>
       <c r="D3" t="n">
-        <v>58.84595739255382</v>
+        <v>34.51334054279662</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.10801760966293</v>
+        <v>32.94058072059322</v>
       </c>
       <c r="C4" t="n">
-        <v>71.25426662652924</v>
+        <v>51.26784686347268</v>
       </c>
       <c r="D4" t="n">
-        <v>51.16574510223102</v>
+        <v>31.06446085777758</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.33476027161494</v>
+        <v>30.23782929080177</v>
       </c>
       <c r="C5" t="n">
-        <v>69.90043654237292</v>
+        <v>45.74944301790137</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20823799095412</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>38.40007970390975</v>
+        <v>19.40129813132547</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37951975538279</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0360012866872</v>
+        <v>18.07094927424221</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6634369655308</v>
+        <v>117.8914309795801</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012000428895734</v>
+        <v>6.884171152092269</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.353470231257857</v>
+        <v>7.944302422765189</v>
       </c>
       <c r="C2" t="n">
-        <v>7.037167544041137</v>
+        <v>8.986918484675302</v>
       </c>
       <c r="D2" t="n">
-        <v>19.90297120819559</v>
+        <v>17.32686523225195</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09084487260522</v>
+        <v>19.67422399310608</v>
       </c>
       <c r="C3" t="n">
-        <v>23.9006478598886</v>
+        <v>25.22109852210056</v>
       </c>
       <c r="D3" t="n">
-        <v>60.00441968356505</v>
+        <v>39.82459562277187</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.39857387239098</v>
+        <v>24.84901614219102</v>
       </c>
       <c r="C4" t="n">
-        <v>60.57186985661971</v>
+        <v>53.74381457358314</v>
       </c>
       <c r="D4" t="n">
-        <v>59.48703864342698</v>
+        <v>35.35273482992764</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.29134238844983</v>
+        <v>24.47006152835176</v>
       </c>
       <c r="C5" t="n">
-        <v>75.49639845657973</v>
+        <v>53.92249265575607</v>
       </c>
       <c r="D5" t="n">
-        <v>37.77274292089604</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>14.89311267342412</v>
       </c>
       <c r="C6" t="n">
-        <v>51.20010627187966</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044199697983129</v>
+        <v>7.06444870493154</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03937216859184</v>
+        <v>66.22920660873319</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402624811239455</v>
+        <v>5.298336528698655</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.28434698133308</v>
+        <v>6.365652114336318</v>
       </c>
       <c r="C2" t="n">
-        <v>5.132576997802325</v>
+        <v>7.780350556155972</v>
       </c>
       <c r="D2" t="n">
-        <v>22.63124807829747</v>
+        <v>26.32360119396973</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.71563732313369</v>
+        <v>24.71549845441345</v>
       </c>
       <c r="C3" t="n">
-        <v>26.16848505669873</v>
+        <v>31.72026832421444</v>
       </c>
       <c r="D3" t="n">
-        <v>62.22316949516284</v>
+        <v>45.06712836344983</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.06522162130357</v>
+        <v>33.25964872447344</v>
       </c>
       <c r="C4" t="n">
-        <v>60.24003913258429</v>
+        <v>59.88268296823845</v>
       </c>
       <c r="D4" t="n">
-        <v>77.13788061808039</v>
+        <v>48.67701467196535</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.61165418194155</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="C5" t="n">
-        <v>97.51209072431446</v>
+        <v>82.22137023067039</v>
       </c>
       <c r="D5" t="n">
-        <v>50.95270585040947</v>
+        <v>36.27557767191965</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.36104647545135</v>
+        <v>25.68055644768807</v>
       </c>
       <c r="C6" t="n">
-        <v>90.48572240502003</v>
+        <v>64.00013283984957</v>
       </c>
       <c r="D6" t="n">
-        <v>37.07177506006381</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>12.75584792127881</v>
       </c>
       <c r="C7" t="n">
-        <v>53.29908286355933</v>
+        <v>33.71616140694821</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8704346652352</v>
+        <v>20.5283444958008</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.261159380489604</v>
+        <v>7.289477780215434</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33452857257964</v>
+        <v>76.53951669226207</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445869535367202</v>
+        <v>6.378293057688505</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.208752408106076</v>
+        <v>5.926810890537994</v>
       </c>
       <c r="C2" t="n">
-        <v>6.270422587024377</v>
+        <v>8.927031874716247</v>
       </c>
       <c r="D2" t="n">
-        <v>26.10172621280995</v>
+        <v>20.94460552240145</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.07120991852029</v>
+        <v>23.21342446691583</v>
       </c>
       <c r="C3" t="n">
-        <v>22.45747873464579</v>
+        <v>30.84651286743478</v>
       </c>
       <c r="D3" t="n">
-        <v>66.48886327011523</v>
+        <v>55.67000356931538</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.74088502600363</v>
+        <v>41.555416825359</v>
       </c>
       <c r="C4" t="n">
-        <v>63.32861741014475</v>
+        <v>70.84585958156258</v>
       </c>
       <c r="D4" t="n">
-        <v>89.47943100816704</v>
+        <v>60.34214089382595</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.17111150464198</v>
+        <v>42.3378697456437</v>
       </c>
       <c r="C5" t="n">
-        <v>105.3169849730766</v>
+        <v>98.83745012504767</v>
       </c>
       <c r="D5" t="n">
-        <v>67.15154297048184</v>
+        <v>45.25856916577796</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>125.4644113596297</v>
+        <v>101.3134178351581</v>
       </c>
       <c r="D6" t="n">
-        <v>44.19631814978292</v>
+        <v>37.75605320992383</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>94.14175085563514</v>
+        <v>66.2345906147153</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>50.48637569089222</v>
+        <v>33.96356182841841</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>24.84999788989526</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.464918445688183</v>
+        <v>7.500884003359889</v>
       </c>
       <c r="C21" t="n">
-        <v>83.98033251399207</v>
+        <v>86.26016603863872</v>
       </c>
       <c r="D21" t="n">
-        <v>6.53180363997716</v>
+        <v>7.500884003359889</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_22_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497617343429</v>
+        <v>10.84497609694095</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907138864153</v>
+        <v>37.78907112210225</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.547676350249478</v>
+        <v>1.306706194352504</v>
       </c>
       <c r="C2" t="n">
-        <v>7.680212290322798</v>
+        <v>1.975276380944582</v>
       </c>
       <c r="D2" t="n">
-        <v>20.775744917271</v>
+        <v>17.39264232843649</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.58372327786613</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C3" t="n">
-        <v>32.96217917008666</v>
+        <v>26.52682296874882</v>
       </c>
       <c r="D3" t="n">
-        <v>59.2042953046039</v>
+        <v>88.52909923045613</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.46982484864026</v>
+        <v>18.28897798241383</v>
       </c>
       <c r="C4" t="n">
-        <v>74.30455674362409</v>
+        <v>81.92390067628359</v>
       </c>
       <c r="D4" t="n">
-        <v>73.89614969865741</v>
+        <v>96.09052004856507</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.2535215585365</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C5" t="n">
-        <v>115.7971417159113</v>
+        <v>88.50455553784997</v>
       </c>
       <c r="D5" t="n">
-        <v>56.10688129770523</v>
+        <v>54.04521111878692</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.01393406097126</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>128.966305420678</v>
+        <v>56.19131160027045</v>
       </c>
       <c r="D6" t="n">
-        <v>42.78751019418875</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.57831581772616</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>107.5563514864636</v>
+        <v>35.03366682604743</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.44074796594459</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>61.00089360337556</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.697757913674099</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.25975418171699</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.659977652883361</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.433212779480101</v>
+        <v>1.489311267342411</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82867717784232</v>
+        <v>7.345436323174635</v>
       </c>
       <c r="D2" t="n">
-        <v>28.49522711576367</v>
+        <v>21.37166577374881</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.34105166846792</v>
+        <v>7.593818492349079</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1803070868787</v>
+        <v>15.27599427808037</v>
       </c>
       <c r="D3" t="n">
-        <v>61.30032665317084</v>
+        <v>82.75151399096364</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.29565459436108</v>
+        <v>20.44587768864407</v>
       </c>
       <c r="C4" t="n">
-        <v>77.50799950258143</v>
+        <v>73.78128521726053</v>
       </c>
       <c r="D4" t="n">
-        <v>84.70617367011906</v>
+        <v>117.6212289504019</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.92311455056183</v>
+        <v>22.43293504203962</v>
       </c>
       <c r="C5" t="n">
-        <v>126.130036303109</v>
+        <v>123.9456476611598</v>
       </c>
       <c r="D5" t="n">
-        <v>67.05336820005716</v>
+        <v>74.98098091185015</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="C6" t="n">
-        <v>153.9223320626319</v>
+        <v>99.98511319131218</v>
       </c>
       <c r="D6" t="n">
-        <v>49.75104666041137</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.77711188006952</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>145.5244622005047</v>
+        <v>59.10808402958771</v>
       </c>
       <c r="D7" t="n">
-        <v>41.56130731158447</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.53525778745954</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>98.63619184567703</v>
+        <v>38.46978379091126</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42499894494763</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>53.91562042182632</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.878757788752676</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4086959773789</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.848447235940844</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.729119749085891</v>
+        <v>0.7795076771719675</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1722888743287</v>
+        <v>2.96095107600838</v>
       </c>
       <c r="D2" t="n">
-        <v>31.33247798103695</v>
+        <v>14.37573163328604</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.14746744428205</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9516009295182</v>
+        <v>23.1937895128309</v>
       </c>
       <c r="D3" t="n">
-        <v>67.11718180083319</v>
+        <v>83.58599953957344</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.34670547498192</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="C4" t="n">
-        <v>76.67842269249287</v>
+        <v>66.30233120630834</v>
       </c>
       <c r="D4" t="n">
-        <v>92.07026319967437</v>
+        <v>130.9199833521292</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.42657119639119</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C5" t="n">
-        <v>131.9714351433775</v>
+        <v>144.1941940612503</v>
       </c>
       <c r="D5" t="n">
-        <v>78.80979695841272</v>
+        <v>87.10556505929826</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.9322123218073</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>174.3701732466845</v>
+        <v>131.5021597407475</v>
       </c>
       <c r="D6" t="n">
-        <v>56.67433147075987</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.07760879302705</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>177.5637985285993</v>
+        <v>59.88660995905543</v>
       </c>
       <c r="D7" t="n">
-        <v>45.15450390912779</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.63115026730623</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>138.4411525143639</v>
+        <v>39.47116644924301</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.86093598336221</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>83.31405542549703</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.042845019806037</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5944746498088</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0589119022333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.90739692063131</v>
+        <v>0.6057383335202819</v>
       </c>
       <c r="C2" t="n">
-        <v>7.596763735461819</v>
+        <v>5.155157195000002</v>
       </c>
       <c r="D2" t="n">
-        <v>25.71000887881547</v>
+        <v>19.98641976305657</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.72732048459342</v>
+        <v>4.864559874542945</v>
       </c>
       <c r="C3" t="n">
-        <v>53.38744015694155</v>
+        <v>16.54735755507999</v>
       </c>
       <c r="D3" t="n">
-        <v>72.08482518432206</v>
+        <v>75.91854996940584</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.02242563294421</v>
+        <v>18.49318150489717</v>
       </c>
       <c r="C4" t="n">
-        <v>107.8322225913569</v>
+        <v>62.33312523803848</v>
       </c>
       <c r="D4" t="n">
-        <v>88.42012523528473</v>
+        <v>143.9507206305971</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.13460691313561</v>
+        <v>28.2252464970958</v>
       </c>
       <c r="C5" t="n">
-        <v>104.1879751131928</v>
+        <v>134.0821927075081</v>
       </c>
       <c r="D5" t="n">
-        <v>55.02695882303374</v>
+        <v>111.3301896615883</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.56988099901544</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="C6" t="n">
-        <v>116.9310603143164</v>
+        <v>183.0645309154943</v>
       </c>
       <c r="D6" t="n">
-        <v>29.7057220351</v>
+        <v>55.02401357992099</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.93657161431823</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>97.31574118346508</v>
+        <v>122.2285709264321</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>61.33468782281948</v>
+        <v>58.24709129296325</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.361324212891832</v>
+        <v>0.3249584901056942</v>
       </c>
       <c r="C2" t="n">
-        <v>3.676645152404305</v>
+        <v>3.106249736236908</v>
       </c>
       <c r="D2" t="n">
-        <v>17.73330878181013</v>
+        <v>14.156801895239</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.9643225919444</v>
+        <v>3.642283982755667</v>
       </c>
       <c r="C3" t="n">
-        <v>42.45077073163208</v>
+        <v>18.82010349041136</v>
       </c>
       <c r="D3" t="n">
-        <v>75.6092994425681</v>
+        <v>74.80917506360696</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.93004353775377</v>
+        <v>15.21316242500857</v>
       </c>
       <c r="C4" t="n">
-        <v>122.956045975279</v>
+        <v>53.74381457358314</v>
       </c>
       <c r="D4" t="n">
-        <v>102.6250327680318</v>
+        <v>149.1579104539222</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.72427743048944</v>
+        <v>29.86967390170921</v>
       </c>
       <c r="C5" t="n">
-        <v>149.5938064346078</v>
+        <v>130.4251825091888</v>
       </c>
       <c r="D5" t="n">
-        <v>68.74688298988291</v>
+        <v>132.3150468398639</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>26.72709950041517</v>
       </c>
       <c r="C6" t="n">
-        <v>141.5248220534032</v>
+        <v>203.9953919700363</v>
       </c>
       <c r="D6" t="n">
-        <v>36.02523200733671</v>
+        <v>68.870583200618</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>126.8398398932794</v>
+        <v>176.126519889582</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>82.69751786723006</v>
+        <v>88.03822537833271</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.707300315414209</v>
+        <v>0.5478152189697202</v>
       </c>
       <c r="C2" t="n">
-        <v>5.228788272818512</v>
+        <v>13.31249886958675</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30781111524377</v>
+        <v>17.390678833028</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.78422079371073</v>
+        <v>2.356194490192345</v>
       </c>
       <c r="C3" t="n">
-        <v>27.61165418194155</v>
+        <v>15.31035544772901</v>
       </c>
       <c r="D3" t="n">
-        <v>72.30080967925635</v>
+        <v>69.79735303342699</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.39172700065703</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="C4" t="n">
-        <v>114.2263453891164</v>
+        <v>50.25959197121121</v>
       </c>
       <c r="D4" t="n">
-        <v>114.8389559565664</v>
+        <v>152.0167597686888</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.80544369477245</v>
+        <v>27.36621725587985</v>
       </c>
       <c r="C5" t="n">
-        <v>188.7655398340555</v>
+        <v>114.9626561673015</v>
       </c>
       <c r="D5" t="n">
-        <v>86.39379797371933</v>
+        <v>152.0236320026186</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.81896717845365</v>
+        <v>32.80509953740717</v>
       </c>
       <c r="C6" t="n">
-        <v>186.002901794305</v>
+        <v>208.4230741161894</v>
       </c>
       <c r="D6" t="n">
-        <v>46.57116584635595</v>
+        <v>88.59389457893643</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.68001666834032</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>164.0893112878119</v>
+        <v>230.9227680021177</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>50.72395863531995</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>121.2507502130023</v>
+        <v>153.6287894990621</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>42.14152020479433</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>74.77186865084555</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.15820991576653</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.970187715974101</v>
+        <v>0.3632466505713198</v>
       </c>
       <c r="C2" t="n">
-        <v>2.45633275602552</v>
+        <v>6.815292562881358</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36372967665683</v>
+        <v>12.52219196766807</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.1488501026138</v>
+        <v>3.563744166415922</v>
       </c>
       <c r="C3" t="n">
-        <v>26.27647730416588</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D3" t="n">
-        <v>71.63812997888975</v>
+        <v>76.09526455617028</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.10117073792898</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="C4" t="n">
-        <v>108.9553419650153</v>
+        <v>70.04180821178444</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6069447031947</v>
+        <v>157.0707969501514</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.62167694762905</v>
+        <v>20.49398332615217</v>
       </c>
       <c r="C5" t="n">
-        <v>225.2129233542184</v>
+        <v>173.8184310368978</v>
       </c>
       <c r="D5" t="n">
-        <v>91.52342972840891</v>
+        <v>139.2363681548039</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>221.8671271781452</v>
+        <v>205.2029416462599</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>73.53977528201584</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>166.5446622961332</v>
+        <v>108.035444366136</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>86.11890861653021</v>
+        <v>55.07604620824605</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.208752408106076</v>
+        <v>0.1855503161026472</v>
       </c>
       <c r="C2" t="n">
-        <v>6.351907646476863</v>
+        <v>3.523492510541802</v>
       </c>
       <c r="D2" t="n">
-        <v>18.2673795329204</v>
+        <v>9.398270772754715</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.09637550593221</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7745421853885</v>
+        <v>28.72593782626167</v>
       </c>
       <c r="D3" t="n">
-        <v>65.49238935030472</v>
+        <v>68.69779560467056</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.54411887899354</v>
+        <v>12.04800782651686</v>
       </c>
       <c r="C4" t="n">
-        <v>88.61156603761286</v>
+        <v>71.87963991413446</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4650332544354</v>
+        <v>152.7442348175358</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.54991155422779</v>
+        <v>19.26679869584366</v>
       </c>
       <c r="C5" t="n">
-        <v>213.5792130588937</v>
+        <v>136.4874745829128</v>
       </c>
       <c r="D5" t="n">
-        <v>109.7839370273996</v>
+        <v>146.5749322440488</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.07935130425731</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>286.4307832002325</v>
+        <v>198.843180018149</v>
       </c>
       <c r="D6" t="n">
-        <v>59.53219903782235</v>
+        <v>79.85928525425255</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>232.1803868112579</v>
+        <v>138.9369351050086</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>140.6942634956104</v>
+        <v>60.58365082907067</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.039490892348125</v>
+        <v>0.3612831551628262</v>
       </c>
       <c r="C2" t="n">
-        <v>4.635812659453438</v>
+        <v>5.471279955767474</v>
       </c>
       <c r="D2" t="n">
-        <v>14.09102479905447</v>
+        <v>11.88209246449915</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87762569433442</v>
+        <v>1.413716694115407</v>
       </c>
       <c r="C3" t="n">
-        <v>21.07321447165778</v>
+        <v>19.89511722656161</v>
       </c>
       <c r="D3" t="n">
-        <v>65.65928646002668</v>
+        <v>60.27440030223293</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.26860762699868</v>
+        <v>8.180903619488671</v>
       </c>
       <c r="C4" t="n">
-        <v>72.22423335832511</v>
+        <v>71.94345351491052</v>
       </c>
       <c r="D4" t="n">
-        <v>131.8644246436146</v>
+        <v>153.063302821416</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.42214548395546</v>
+        <v>19.19316761802515</v>
       </c>
       <c r="C5" t="n">
-        <v>201.9945901487813</v>
+        <v>135.8738822677586</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1785017935156</v>
+        <v>168.9587799008761</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.01521890831177</v>
+        <v>18.87802660496192</v>
       </c>
       <c r="C6" t="n">
-        <v>317.5453131909266</v>
+        <v>209.3488622012941</v>
       </c>
       <c r="D6" t="n">
-        <v>70.96366930607222</v>
+        <v>106.4656297870454</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>293.6240486292488</v>
+        <v>218.6460129605114</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>49.70588626601601</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>182.0012981517949</v>
+        <v>123.6707583039707</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>66.22968187619405</v>
+        <v>52.69530802544753</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.825289966373073</v>
+        <v>0.2856885819358218</v>
       </c>
       <c r="C2" t="n">
-        <v>15.89547707946011</v>
+        <v>14.65945671981337</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21298249855933</v>
+        <v>13.39398392903924</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.27461161974862</v>
+        <v>1.305724446648258</v>
       </c>
       <c r="C3" t="n">
-        <v>19.68895020866978</v>
+        <v>20.57252314249191</v>
       </c>
       <c r="D3" t="n">
-        <v>62.03172869283472</v>
+        <v>55.99888905023806</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.40226418349649</v>
+        <v>5.411393345808419</v>
       </c>
       <c r="C4" t="n">
-        <v>62.83087132409162</v>
+        <v>60.15070009149782</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4470019428604</v>
+        <v>149.0302832523701</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.61849502480483</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="C5" t="n">
-        <v>172.3458094805276</v>
+        <v>132.9531828476243</v>
       </c>
       <c r="D5" t="n">
-        <v>136.1193191938203</v>
+        <v>182.6541603751191</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.45927197026759</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="C6" t="n">
-        <v>320.1214191668702</v>
+        <v>213.6155377239508</v>
       </c>
       <c r="D6" t="n">
-        <v>86.17879522648927</v>
+        <v>132.8304643845935</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.71049190490098</v>
+        <v>15.15131231964102</v>
       </c>
       <c r="C7" t="n">
-        <v>362.972742961835</v>
+        <v>262.1835784007447</v>
       </c>
       <c r="D7" t="n">
-        <v>49.28667999630262</v>
+        <v>66.2345906147153</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>259.7753512822273</v>
+        <v>205.1999964031471</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>123.5843645059969</v>
+        <v>100.8421789371196</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>47.26133448244146</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.841799750896022</v>
+        <v>4.564145077043421</v>
       </c>
       <c r="C2" t="n">
-        <v>3.264311116620644</v>
+        <v>7.095090658591698</v>
       </c>
       <c r="D2" t="n">
-        <v>8.681594948654544</v>
+        <v>8.213301293728815</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.491094836301658</v>
+        <v>0.9562222639363932</v>
       </c>
       <c r="C2" t="n">
-        <v>9.155779089805753</v>
+        <v>24.84116216055704</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8059170541954</v>
+        <v>19.87057353395544</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24716374175872</v>
+        <v>1.124101121362598</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8127735925919</v>
+        <v>38.41578766717769</v>
       </c>
       <c r="D3" t="n">
-        <v>67.81913140936966</v>
+        <v>53.72614311490671</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.58164627593317</v>
+        <v>3.969205968269854</v>
       </c>
       <c r="C4" t="n">
-        <v>93.6145523384546</v>
+        <v>55.24981555189775</v>
       </c>
       <c r="D4" t="n">
-        <v>136.1271731754542</v>
+        <v>142.5340586933689</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.70602513473626</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>265.7836472322178</v>
+        <v>122.3748513343649</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7492981203105</v>
+        <v>193.0606860401353</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.78243722475149</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>298.6672865859647</v>
+        <v>213.4947827563284</v>
       </c>
       <c r="D6" t="n">
-        <v>70.44039777970866</v>
+        <v>153.7613254391355</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>182.6541603751191</v>
+        <v>282.9043454465778</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>84.85932631198153</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>91.04237335332795</v>
+        <v>270.9574576335984</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>42.55876297909923</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>36.0546844384641</v>
+        <v>168.1812357191125</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>75.16260423713581</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.214863878509809</v>
+        <v>4.887140071740622</v>
       </c>
       <c r="C2" t="n">
-        <v>7.652723354603888</v>
+        <v>5.106069809787661</v>
       </c>
       <c r="D2" t="n">
-        <v>12.15207308316702</v>
+        <v>23.77203891063226</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.52986602285279</v>
+        <v>7.539822368615503</v>
       </c>
       <c r="C3" t="n">
-        <v>8.222137023067038</v>
+        <v>14.00953973960199</v>
       </c>
       <c r="D3" t="n">
-        <v>10.42616061910113</v>
+        <v>8.6491972744144</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39877724830932</v>
+        <v>11.67842636015255</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14653971173701</v>
+        <v>59.94925531544978</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576326735095213</v>
+        <v>0.7785617573435035</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.774239085752239</v>
+        <v>2.294344384824796</v>
       </c>
       <c r="C2" t="n">
-        <v>6.924266558052754</v>
+        <v>5.363287708300325</v>
       </c>
       <c r="D2" t="n">
-        <v>13.27519245682537</v>
+        <v>28.86338250485622</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.78359889890498</v>
+        <v>13.50884841043611</v>
       </c>
       <c r="C3" t="n">
-        <v>21.97642235956485</v>
+        <v>17.98070920328033</v>
       </c>
       <c r="D3" t="n">
-        <v>18.11324514335365</v>
+        <v>27.39566968700725</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.83402788472006</v>
+        <v>9.393362034233482</v>
       </c>
       <c r="C4" t="n">
-        <v>13.27322896141688</v>
+        <v>23.3302524437212</v>
       </c>
       <c r="D4" t="n">
-        <v>20.53521672973053</v>
+        <v>18.73567318784613</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4436413288139</v>
+        <v>13.62975416812183</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15926215022493</v>
+        <v>73.76102255689462</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251292911329243</v>
+        <v>1.603500490367274</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.32794479094744</v>
+        <v>1.910481032464293</v>
       </c>
       <c r="C2" t="n">
-        <v>8.70417514585222</v>
+        <v>4.548437113775472</v>
       </c>
       <c r="D2" t="n">
-        <v>20.32021398250048</v>
+        <v>25.54998400302324</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38813450054276</v>
+        <v>10.29362467902781</v>
       </c>
       <c r="C3" t="n">
-        <v>24.99038781160256</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="D3" t="n">
-        <v>24.52896639060656</v>
+        <v>45.01804097823749</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.00515508489526</v>
+        <v>19.55248727777947</v>
       </c>
       <c r="C4" t="n">
-        <v>37.8414652601933</v>
+        <v>36.782159487311</v>
       </c>
       <c r="D4" t="n">
-        <v>25.00216878405352</v>
+        <v>28.74164578952962</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.75075925630833</v>
+        <v>8.860273030827464</v>
       </c>
       <c r="C5" t="n">
-        <v>16.24792450528471</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>26.48264432205772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74092802761664</v>
+        <v>14.84089282325978</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1196609684615</v>
+        <v>87.39636884808539</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022278408284992</v>
+        <v>2.473482137209964</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.143196296099792</v>
+        <v>1.920298509506761</v>
       </c>
       <c r="C2" t="n">
-        <v>6.299875018151782</v>
+        <v>5.450663253978291</v>
       </c>
       <c r="D2" t="n">
-        <v>20.38991806950201</v>
+        <v>38.12715384212913</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31941216124548</v>
+        <v>8.202502068982101</v>
       </c>
       <c r="C3" t="n">
-        <v>30.05129722699487</v>
+        <v>18.54030539470102</v>
       </c>
       <c r="D3" t="n">
-        <v>34.51334054279662</v>
+        <v>55.01223260747002</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.94058072059322</v>
+        <v>20.06299608398782</v>
       </c>
       <c r="C4" t="n">
-        <v>51.26784686347268</v>
+        <v>44.55465606183299</v>
       </c>
       <c r="D4" t="n">
-        <v>31.06446085777758</v>
+        <v>44.54189334167778</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.23782929080177</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>45.74944301790137</v>
+        <v>51.14905539125883</v>
       </c>
       <c r="D5" t="n">
-        <v>32.22586839190156</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.92078153559227</v>
+        <v>8.412596077690921</v>
       </c>
       <c r="C6" t="n">
-        <v>19.40129813132547</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07094927424221</v>
+        <v>16.08622794319945</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8914309795801</v>
+        <v>101.5972291149439</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884171152092269</v>
+        <v>3.386574303831464</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.944302422765189</v>
+        <v>3.75813021185679</v>
       </c>
       <c r="C2" t="n">
-        <v>8.986918484675302</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="D2" t="n">
-        <v>17.32686523225195</v>
+        <v>31.72026832421444</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67422399310608</v>
+        <v>7.314020396638738</v>
       </c>
       <c r="C3" t="n">
-        <v>25.22109852210056</v>
+        <v>20.07674055184727</v>
       </c>
       <c r="D3" t="n">
-        <v>39.82459562277187</v>
+        <v>71.75103096487814</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.84901614219102</v>
+        <v>17.76570645605028</v>
       </c>
       <c r="C4" t="n">
-        <v>53.74381457358314</v>
+        <v>45.6139618347153</v>
       </c>
       <c r="D4" t="n">
-        <v>35.35273482992764</v>
+        <v>60.712259778327</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.47006152835176</v>
+        <v>25.35363446217388</v>
       </c>
       <c r="C5" t="n">
-        <v>53.92249265575607</v>
+        <v>68.30509652297184</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>40.17802479630072</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>31.79880814055419</v>
+        <v>56.714583126634</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>15.92983824910874</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06444870493154</v>
+        <v>17.35782560384647</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22920660873319</v>
+        <v>115.429540265579</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298336528698655</v>
+        <v>4.339456400961618</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.365652114336318</v>
+        <v>2.984513020910303</v>
       </c>
       <c r="C2" t="n">
-        <v>7.780350556155972</v>
+        <v>7.838273670706534</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32360119396973</v>
+        <v>32.11983963984289</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.71549845441345</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C3" t="n">
-        <v>31.72026832421444</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D3" t="n">
-        <v>45.06712836344983</v>
+        <v>79.32030576462104</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.25964872447344</v>
+        <v>15.74919667152733</v>
       </c>
       <c r="C4" t="n">
-        <v>59.88268296823845</v>
+        <v>47.56665801846221</v>
       </c>
       <c r="D4" t="n">
-        <v>48.67701467196535</v>
+        <v>80.02225537315752</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.47130531796326</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="C5" t="n">
-        <v>82.22137023067039</v>
+        <v>76.55177723864504</v>
       </c>
       <c r="D5" t="n">
-        <v>36.27557767191965</v>
+        <v>52.17989048071799</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.68055644768807</v>
+        <v>25.51954982419159</v>
       </c>
       <c r="C6" t="n">
-        <v>64.00013283984957</v>
+        <v>82.63664950956678</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.75584792127881</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="C7" t="n">
-        <v>33.71616140694821</v>
+        <v>55.51488743204438</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>20.5283444958008</v>
+        <v>33.12907627980861</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289477780215434</v>
+        <v>18.65129893425972</v>
       </c>
       <c r="C21" t="n">
-        <v>76.53951669226207</v>
+        <v>128.7827783556028</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378293057688505</v>
+        <v>5.328942552645635</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.926810890537994</v>
+        <v>2.701769682087222</v>
       </c>
       <c r="C2" t="n">
-        <v>8.927031874716247</v>
+        <v>4.765403356414017</v>
       </c>
       <c r="D2" t="n">
-        <v>20.94460552240145</v>
+        <v>25.22895250373453</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.21342446691583</v>
+        <v>12.32093368829747</v>
       </c>
       <c r="C3" t="n">
-        <v>30.84651286743478</v>
+        <v>35.47054455443726</v>
       </c>
       <c r="D3" t="n">
-        <v>55.67000356931538</v>
+        <v>87.04666019704344</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.555416825359</v>
+        <v>12.64785567381166</v>
       </c>
       <c r="C4" t="n">
-        <v>70.84585958156258</v>
+        <v>68.34436643114171</v>
       </c>
       <c r="D4" t="n">
-        <v>60.34214089382595</v>
+        <v>72.5050132017397</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.3378697456437</v>
+        <v>14.35806017460961</v>
       </c>
       <c r="C5" t="n">
-        <v>98.83745012504767</v>
+        <v>49.3573658310084</v>
       </c>
       <c r="D5" t="n">
-        <v>45.25856916577796</v>
+        <v>39.76078202199582</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>8.93586760405447</v>
       </c>
       <c r="C6" t="n">
-        <v>101.3134178351581</v>
+        <v>36.54850353370026</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>66.2345906147153</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>33.96356182841841</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>24.84999788989526</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500884003359889</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.26016603863872</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500884003359889</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
